--- a/AtchisonRegime/Outputs/China/ASX300_Materials/df_regTrendSummaryASX300_Materials.xlsx
+++ b/AtchisonRegime/Outputs/China/ASX300_Materials/df_regTrendSummaryASX300_Materials.xlsx
@@ -780,13 +780,13 @@
         <v>45626</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06524666334535389</v>
+        <v>-0.06648430172808162</v>
       </c>
     </row>
   </sheetData>
